--- a/r5-core-76-add-healthcare-service/all-profiles.xlsx
+++ b/r5-core-76-add-healthcare-service/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T20:03:30+00:00</t>
+    <t>2026-10-12T11:43:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -573,7 +573,7 @@
     <t>Collection of specialties handled by the Healthcare service. This is more of a medical term.</t>
   </si>
   <si>
-    <t>extensible</t>
+    <t>preferred</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/core/r5/ValueSet/at-funktionscode-vs</t>
@@ -1392,6 +1392,9 @@
     <t>Extension.extension.value[x]</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/ValueSet/elga-religiousaffiliation</t>
   </si>
   <si>
@@ -1498,9 +1501,6 @@
   </si>
   <si>
     <t>If no purpose is defined, then these contact details may be used for any purpose.</t>
-  </si>
-  <si>
-    <t>preferred</t>
   </si>
   <si>
     <t>The purpose for which an extended contact detail should be used.</t>
@@ -7608,7 +7608,7 @@
         <v>2</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="149">
@@ -7616,7 +7616,7 @@
         <v>4</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="150">
@@ -7632,7 +7632,7 @@
         <v>8</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="152">
@@ -7640,7 +7640,7 @@
         <v>10</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="153">
@@ -7702,7 +7702,7 @@
         <v>24</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="161">
@@ -7770,7 +7770,7 @@
         <v>386</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="170">
@@ -7778,7 +7778,7 @@
         <v>386</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="171">
@@ -7786,7 +7786,7 @@
         <v>386</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="172">
@@ -7794,7 +7794,7 @@
         <v>386</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="173">
@@ -7810,7 +7810,7 @@
         <v>2</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="175">
@@ -7818,7 +7818,7 @@
         <v>4</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="176">
@@ -7834,7 +7834,7 @@
         <v>8</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="178">
@@ -7842,7 +7842,7 @@
         <v>10</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="179">
@@ -7904,7 +7904,7 @@
         <v>24</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="187">
@@ -7940,7 +7940,7 @@
         <v>32</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="192">
@@ -7948,7 +7948,7 @@
         <v>34</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="193">
@@ -17539,11 +17539,11 @@
         <v>23</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z82" s="2"/>
       <c r="AA82" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AB82" t="s" s="2">
         <v>23</v>
@@ -17581,13 +17581,13 @@
         <v>420</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>390</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E83" t="s" s="2">
         <v>23</v>
@@ -17612,7 +17612,7 @@
         <v>129</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>325</v>
@@ -17686,7 +17686,7 @@
         <v>420</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>432</v>
@@ -17789,7 +17789,7 @@
         <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>434</v>
@@ -17892,7 +17892,7 @@
         <v>420</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>436</v>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="R86" s="2"/>
       <c r="S86" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>23</v>
@@ -17997,7 +17997,7 @@
         <v>420</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>438</v>
@@ -18231,7 +18231,7 @@
         <v>23</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M89" t="s" s="2">
         <v>396</v>
@@ -18305,7 +18305,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>324</v>
@@ -18337,10 +18337,10 @@
         <v>78</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -18408,7 +18408,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>389</v>
@@ -18511,7 +18511,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>390</v>
@@ -18614,7 +18614,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>391</v>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="R93" s="2"/>
       <c r="S93" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>23</v>
@@ -18719,7 +18719,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>395</v>
@@ -18748,7 +18748,7 @@
         <v>23</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>396</v>
@@ -18822,13 +18822,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -18854,13 +18854,13 @@
         <v>78</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P95" s="2"/>
       <c r="Q95" t="s" s="2">
@@ -18910,7 +18910,7 @@
         <v>23</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>76</v>
@@ -18927,13 +18927,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -19030,13 +19030,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -19135,13 +19135,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -19167,13 +19167,13 @@
         <v>162</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
@@ -19199,7 +19199,7 @@
         <v>23</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>474</v>
+        <v>178</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>475</v>
@@ -19223,7 +19223,7 @@
         <v>23</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>76</v>
@@ -19240,7 +19240,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>477</v>
@@ -19345,7 +19345,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>482</v>
@@ -19448,7 +19448,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>486</v>
@@ -19553,7 +19553,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>491</v>
@@ -19658,7 +19658,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>495</v>
@@ -21297,7 +21297,7 @@
         <v>23</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z118" t="s" s="2">
         <v>543</v>
@@ -22135,7 +22135,7 @@
         <v>23</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z126" t="s" s="2">
         <v>591</v>
@@ -22551,7 +22551,7 @@
         <v>23</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>474</v>
+        <v>178</v>
       </c>
       <c r="Z130" t="s" s="2">
         <v>616</v>
@@ -23078,7 +23078,7 @@
         <v>23</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z135" t="s" s="2">
         <v>639</v>
@@ -26335,7 +26335,7 @@
         <v>23</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z166" t="s" s="2">
         <v>543</v>
@@ -27173,7 +27173,7 @@
         <v>23</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z174" t="s" s="2">
         <v>591</v>
@@ -27912,7 +27912,7 @@
         <v>23</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z181" t="s" s="2">
         <v>543</v>
@@ -28750,7 +28750,7 @@
         <v>23</v>
       </c>
       <c r="Y189" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z189" t="s" s="2">
         <v>591</v>
@@ -29489,7 +29489,7 @@
         <v>23</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z196" t="s" s="2">
         <v>543</v>
@@ -30327,7 +30327,7 @@
         <v>23</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z204" t="s" s="2">
         <v>591</v>
@@ -31066,7 +31066,7 @@
         <v>23</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z211" t="s" s="2">
         <v>543</v>
@@ -31904,7 +31904,7 @@
         <v>23</v>
       </c>
       <c r="Y219" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z219" t="s" s="2">
         <v>591</v>
@@ -32330,7 +32330,7 @@
         <v>23</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z223" s="2"/>
       <c r="AA223" t="s" s="2">
@@ -35462,7 +35462,7 @@
         <v>23</v>
       </c>
       <c r="Y253" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z253" s="2"/>
       <c r="AA253" t="s" s="2">
@@ -35510,7 +35510,7 @@
         <v>896</v>
       </c>
       <c r="D254" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E254" t="s" s="2">
         <v>23</v>
@@ -35858,7 +35858,7 @@
       </c>
       <c r="R257" s="2"/>
       <c r="S257" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T257" t="s" s="2">
         <v>23</v>
@@ -36154,7 +36154,7 @@
         <v>23</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M260" t="s" s="2">
         <v>396</v>
@@ -36706,11 +36706,11 @@
         <v>23</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z265" s="2"/>
       <c r="AA265" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AB265" t="s" s="2">
         <v>23</v>
@@ -37855,7 +37855,7 @@
         <v>23</v>
       </c>
       <c r="Y276" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z276" s="2"/>
       <c r="AA276" t="s" s="2">
@@ -40797,7 +40797,7 @@
         <v>23</v>
       </c>
       <c r="Y304" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z304" t="s" s="2">
         <v>591</v>
@@ -43531,7 +43531,7 @@
         <v>23</v>
       </c>
       <c r="Y330" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z330" t="s" s="2">
         <v>591</v>
@@ -51507,7 +51507,7 @@
         <v>23</v>
       </c>
       <c r="Y406" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z406" t="s" s="2">
         <v>1251</v>
@@ -53623,7 +53623,7 @@
         <v>23</v>
       </c>
       <c r="Y426" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z426" t="s" s="2">
         <v>1293</v>
@@ -62532,7 +62532,7 @@
         <v>23</v>
       </c>
       <c r="Y511" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z511" s="2"/>
       <c r="AA511" t="s" s="2">
@@ -63479,7 +63479,7 @@
         <v>23</v>
       </c>
       <c r="Y520" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z520" t="s" s="2">
         <v>543</v>
@@ -64317,7 +64317,7 @@
         <v>23</v>
       </c>
       <c r="Y528" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z528" t="s" s="2">
         <v>591</v>
@@ -65056,7 +65056,7 @@
         <v>23</v>
       </c>
       <c r="Y535" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z535" t="s" s="2">
         <v>543</v>
@@ -65894,7 +65894,7 @@
         <v>23</v>
       </c>
       <c r="Y543" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z543" t="s" s="2">
         <v>591</v>
@@ -66633,7 +66633,7 @@
         <v>23</v>
       </c>
       <c r="Y550" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z550" t="s" s="2">
         <v>543</v>
@@ -67471,7 +67471,7 @@
         <v>23</v>
       </c>
       <c r="Y558" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z558" t="s" s="2">
         <v>591</v>
@@ -71992,7 +71992,7 @@
         <v>23</v>
       </c>
       <c r="Y601" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z601" s="2"/>
       <c r="AA601" t="s" s="2">
@@ -72095,7 +72095,7 @@
         <v>23</v>
       </c>
       <c r="Y602" t="s" s="2">
-        <v>474</v>
+        <v>178</v>
       </c>
       <c r="Z602" t="s" s="2">
         <v>1611</v>
@@ -74195,7 +74195,7 @@
         <v>23</v>
       </c>
       <c r="Y622" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z622" s="2"/>
       <c r="AA622" t="s" s="2">
@@ -75253,7 +75253,7 @@
         <v>23</v>
       </c>
       <c r="Y632" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z632" t="s" s="2">
         <v>1730</v>
@@ -79243,7 +79243,7 @@
         <v>23</v>
       </c>
       <c r="Y670" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z670" t="s" s="2">
         <v>1859</v>
@@ -79348,7 +79348,7 @@
         <v>23</v>
       </c>
       <c r="Y671" t="s" s="2">
-        <v>178</v>
+        <v>439</v>
       </c>
       <c r="Z671" t="s" s="2">
         <v>1859</v>
